--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260818.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>43,831,027</t>
+          <t>43,661,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>64.20%</t>
+          <t>64.57%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,646,703</t>
+          <t>2,636,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.54%</t>
+          <t>6.37%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,954,000</t>
+          <t>21,868,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,965,267</t>
+          <t>5,942,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>523,000</t>
+          <t>521,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,371,901</t>
+          <t>2,362,901</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>20,972,286</t>
+          <t>20,890,286</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>575,222</t>
+          <t>573,222</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,831,608</t>
+          <t>2,820,608</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>4,752,285</t>
+          <t>4,733,285</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,213,617</t>
+          <t>1,208,617</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,051,288</t>
+          <t>2,043,288</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,562,296</t>
+          <t>5,407,520</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,428,520</t>
+          <t>5,540,296</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -941,78 +941,78 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,516,000</t>
+          <t>3,503,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>144,482</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>156,499</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>156,499</t>
+          <t>143,482</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1029,100 +1029,100 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>321,672</t>
+          <t>320,672</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,371,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>615,600</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13,197,134</t>
+          <t>1,366,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>617,600</t>
+          <t>13,145,134</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>878,349</t>
+          <t>875,349</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>141,921</t>
+          <t>825,897</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>828,897</t>
+          <t>140,921</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>592,000</t>
+          <t>590,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,026,822</t>
+          <t>1,022,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,39 +1239,39 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,052,587</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2,044,587</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>202609WTEU6F</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>385,000</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1315,56 +1315,56 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,863,000</t>
+          <t>5,840,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,302,000</t>
+          <t>1,871,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,878,000</t>
+          <t>3,289,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1381,29 +1381,29 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>788,000</t>
+          <t>785,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,226,441</t>
+          <t>956,659</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,39 +1415,39 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>959,659</t>
+          <t>3,552,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,566,981</t>
+          <t>1,221,441</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,61 +1459,61 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,347,249</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,564,578</t>
+          <t>2,651,703</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,864,121</t>
+          <t>7,318,249</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>4,546,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,413,384</t>
+          <t>1,407,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,661,703</t>
+          <t>10,821,121</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>597,000</t>
+          <t>594,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>149,386</t>
+          <t>148,386</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>399,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,245,107</t>
+          <t>398,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,39 +1679,39 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,214,076</t>
+          <t>2,236,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,39 +1723,39 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>1,210,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5,083,956</t>
+          <t>792,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>824,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>296,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>233,000</t>
+          <t>5,063,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,61 +1833,61 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,598,400</t>
+          <t>821,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>298,000</t>
+          <t>232,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>1,592,400</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,61 +1899,61 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>508,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>1,028,121</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,801,000</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>1,794,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,39 +1987,39 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1,024,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>66,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>161,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>339,000</t>
+          <t>338,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,39 +2075,39 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>67,538</t>
+          <t>174,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>694,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>260,000</t>
+          <t>259,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,39 +2163,39 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>697,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>117,000</t>
+          <t>343,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2229,39 +2229,35 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>344,000</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
+          <t>232,960,164</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>236,800,588</t>
+          <t>340,214,610</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2269,17 +2265,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>352,715,853</t>
+          <t>1,073,145,423</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -2287,38 +2283,20 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>1,175,128,968</t>
+          <t>1,054,762,720</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>1,162,177,636</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
